--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -431,6 +431,25 @@
   </sheetPr>
   <dimension ref="A1:Q135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.545674</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0.764472</v>
@@ -7393,10 +7393,10 @@
         <v>0.369371</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>1.376516</v>
+        <v>1.137347</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>1.150091</v>
+        <v>1.176033</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
@@ -17226,7 +17226,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -41881,7 +41885,11 @@
           <t>Exploration and evaluation asset recovery (expenditures)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -1029,28 +1029,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.017598</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00177</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007349</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001894</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>4.3e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000238</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000115</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2005,28 +2005,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.51515</v>
+        <v>-2.532748</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.271528</v>
+        <v>-6.273298</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.056344</v>
+        <v>-3.063693</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.417113</v>
+        <v>-1.419007</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.800552</v>
+        <v>-1.800595</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.387172</v>
+        <v>-1.38741</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.865372</v>
+        <v>-0.865487</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.31054</v>
+        <v>-1.310542</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-2.32974</v>
@@ -2121,28 +2121,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.51515</v>
+        <v>-2.532748</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.271528</v>
+        <v>-6.273298</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.055867</v>
+        <v>-3.063216</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.415946</v>
+        <v>-1.41784</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.799765</v>
+        <v>-1.799808</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.38679</v>
+        <v>-1.387028</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.865256</v>
+        <v>-0.865371</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.31054</v>
+        <v>-1.310542</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.32974</v>
@@ -2412,19 +2412,19 @@
         <v>0.046643</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.011172</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.027134</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.037973</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.342334</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.103902</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.372343</v>
@@ -2528,19 +2528,19 @@
         <v>0.046643</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.011172</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.027134</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.037973</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.342334</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.103902</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.462868</v>
@@ -3224,19 +3224,19 @@
         <v>0.08515200000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.014263</v>
+        <v>0.003091</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.097012</v>
+        <v>0.069878</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.040836</v>
+        <v>0.002863</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.346561</v>
+        <v>0.004227</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.111137</v>
+        <v>0.007235</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.124771</v>
@@ -7747,25 +7747,25 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.493057</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.651</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.723</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-1.012</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.363</v>
       </c>
     </row>
     <row r="125">
@@ -7805,25 +7805,25 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.493057</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.651</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.723</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-1.012</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.363</v>
       </c>
     </row>
     <row r="126">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -26303,7 +26303,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -30834,7 +30838,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -33531,7 +33539,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -35646,7 +35658,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -39545,7 +39561,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -64010,7 +64030,11 @@
           <t>General and administrative – Note 16</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -68305,7 +68329,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -71515,7 +71539,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -73859,7 +73883,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -77849,7 +77873,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E696" s="5" t="n">

--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.294303</v>
+        <v>0.564303</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.295318</v>
+        <v>0.560318</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.103928</v>
+        <v>0.296428</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.08637499999999999</v>
+        <v>0.266375</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.079365</v>
+        <v>0.259365</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08962299999999999</v>
+        <v>0.269623</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.075446</v>
+        <v>0.260446</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.055518</v>
+        <v>0.262505</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.214577</v>
@@ -855,28 +855,28 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.095319</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.07638499999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.314255</v>
+        <v>0.403388</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.254086</v>
+        <v>0.341556</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.302806</v>
+        <v>0.330418</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.366275</v>
+        <v>0.476529</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.369075</v>
+        <v>0.434454</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.360087</v>
+        <v>0.389887</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.504375</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.294303</v>
+        <v>0.659622</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.295318</v>
+        <v>0.636703</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.980818</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.294303</v>
+        <v>-0.659622</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.295318</v>
+        <v>-0.636703</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.980818</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.064757</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0.115</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>0.060315</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>0.020076</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1799,43 +1799,31 @@
         <v>-0.031</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.213</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.258</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>-0.39</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>-0.33</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.03</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.62</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>-0.41</v>
@@ -1869,43 +1857,31 @@
         <v>-0.031</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.213</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.258</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>-0.39</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>-0.33</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.03</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-0.62</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>-0.41</v>
@@ -1939,43 +1915,31 @@
         <v>98.621419</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>111.679407</v>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>120.61376</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6.653113</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>6.978884</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>22.373742</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>41.20819</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>3.360359</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>7.059818</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>16.44564</v>
-      </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>54.8188</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>71.881597</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>82.79512200000001</v>
@@ -2035,7 +1999,7 @@
         <v>-1.644564</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-44.56659</v>
+        <v>-44.501833</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-34.061</v>
@@ -2090,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.046391</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>2.168167</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>3.182</v>
@@ -2148,10 +2112,10 @@
         <v>-2.32974</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.644564</v>
+        <v>-1.598173</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-44.56659</v>
+        <v>-42.333666</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-30.879</v>
@@ -2224,10 +2188,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-9723.668184236978</v>
+        <v>-9449.376219476144</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-972220.5497382199</v>
+        <v>-923509.2931937174</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-308790</v>
@@ -2601,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>0.352111</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>0.654244</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>0.289</v>
@@ -2809,13 +2773,13 @@
         <v>0.006423</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.011537</v>
+        <v>0.017803</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.00686</v>
+        <v>0.028223</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.080933</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0.009382</v>
@@ -2836,7 +2800,7 @@
         <v>0.2</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.654244</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.289</v>
@@ -3215,13 +3179,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.014767</v>
+        <v>0.008501</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.071464</v>
+        <v>0.050101</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.08515200000000001</v>
+        <v>0.004219</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.003091</v>
@@ -3242,7 +3206,7 @@
         <v>0.124771</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.946512</v>
+        <v>0.292268</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.5610000000000001</v>
@@ -3504,22 +3468,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.004937</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.003677</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.001632</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.001285</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.000498</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>0.000116</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -3858,7 +3822,7 @@
         <v>0.179395</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>5.488628</v>
+        <v>6.65794</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>4.737</v>
@@ -4324,7 +4288,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.056312</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -4449,19 +4413,19 @@
         <v>0.203306</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.391854</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.92635</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.9495170000000001</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>1.046166</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>1.37108</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0.808399</v>
@@ -4507,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>0.119884</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>0.294884</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -4623,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.119884</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.294884</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -4855,19 +4819,19 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.5147080000000001</v>
+        <v>0.00297</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.235615</v>
+        <v>0.014381</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.949864</v>
+        <v>0.000347</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.046513</v>
+        <v>0.000347</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1.40858</v>
+        <v>0.0375</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -5150,15 +5114,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>0.04744050250114858</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.3271084330666998</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
@@ -5664,28 +5624,28 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>8.897273999999999</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>13.397112</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>15.223747</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>15.448918</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>15.623918</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>17.185899</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>17.885515</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>18.83902</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>19.701208</v>
@@ -5896,28 +5856,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.615501</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.946131</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.81874</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.014962</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.014962</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.374867</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.436609</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.468102</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>2.545674</v>
@@ -6352,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.046391</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>2.168167</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>3.182</v>
@@ -14636,7 +14596,11 @@
           <t>Accounts receivable – Note 9</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14939,7 +14903,11 @@
           <t>Patents – Note 12</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Patents</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15040,7 +15008,11 @@
           <t>Right-of-use assets – Note 11</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -18028,7 +18000,11 @@
           <t>Accounts payable and accrued liabilities – Notes 5 and 10 $</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18127,7 +18103,11 @@
           <t>Interest payable – Note 6</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -18228,7 +18208,11 @@
           <t>Loans payable – Note 6</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18428,7 +18412,11 @@
           <t>Loans payable – Note 6</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -18529,7 +18517,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -18628,7 +18620,11 @@
           <t>Reserves – Note 8</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19335,7 +19331,11 @@
           <t>Accounts payable and accrued liabilities – Notes 6 and 11 $</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -19430,7 +19430,11 @@
           <t>Interest payable – Note 7</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19630,7 +19634,11 @@
           <t>Share capital – Note 9</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -19723,7 +19731,11 @@
           <t>Reserves – Note 9</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -20301,7 +20313,11 @@
           <t>Equipment – Note 4</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20501,7 +20517,11 @@
           <t>Interest payable – Notes 7 and 11</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -20600,7 +20620,11 @@
           <t>Loans payable – Notes 7 and 11</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -20701,7 +20725,11 @@
           <t>Receivables – Note 4</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -20800,7 +20828,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -21002,7 +21034,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 11 $</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -21101,7 +21137,11 @@
           <t>Interest payable – Notes 8 and 11</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -21200,7 +21240,11 @@
           <t>Loans payable – Notes 8 and 11</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -21400,7 +21444,11 @@
           <t>Receivables – Note 5</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21497,7 +21545,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -21695,7 +21747,11 @@
           <t>Accounts payable and accrued liabilities – Notes 8 and 13 $</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -21792,7 +21848,11 @@
           <t>Interest payable – Notes 9 and 13</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>InterestPayable</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21893,7 +21953,11 @@
           <t>Loans payable – Notes 9 and 13</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -22196,7 +22260,11 @@
           <t>Share capital – Note 11</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -22293,7 +22361,11 @@
           <t>Reserves – Note 11</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -22794,7 +22866,11 @@
           <t>Equipment - Note 4</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -23196,7 +23272,11 @@
           <t>Share capital - Note 8</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -23295,7 +23375,11 @@
           <t>Contributed surplus - Note 8</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -23800,7 +23884,11 @@
           <t>Equipment – Note 4</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
         <v>0.004937</v>
       </c>
@@ -24101,7 +24189,11 @@
           <t>Due to related parties – Note 6</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>0.056312</v>
       </c>
@@ -24301,7 +24393,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>8.897273999999999</v>
       </c>
@@ -24400,7 +24496,11 @@
           <t>Contributed surplus – Note 8</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
         <v>1.615501</v>
       </c>
@@ -38258,7 +38358,11 @@
           <t>Depreciation and amortization – Note 10,11 and 12</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -48087,7 +48191,11 @@
           <t>Cash and cash equivalents, end of the year – Note 4 $</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -64232,7 +64340,11 @@
           <t>Depreciation and amortization – Note 10,11 and 12</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E559" t="inlineStr">
         <is>
           <t>-</t>
@@ -64634,7 +64746,11 @@
           <t>Net finance income – Note 14</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E563" t="inlineStr">
         <is>
           <t>-</t>
@@ -64939,7 +65055,11 @@
           <t>Loss per share: Basic and diluted – Note 15 $</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -70947,7 +71067,11 @@
           <t>Management fees – Note 10</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -71139,7 +71263,11 @@
           <t>Professional fees – Note 10</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>-</t>
@@ -71339,7 +71467,11 @@
           <t>Travel and promotion – Note 10</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
@@ -71632,7 +71764,11 @@
           <t>Interest expense – Note 6</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
@@ -71929,7 +72065,11 @@
           <t>Other income – Note 10</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
@@ -72325,7 +72465,11 @@
           <t>Loss per share – basic and diluted – Note 9 $</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
           <t>-</t>
@@ -72523,7 +72667,11 @@
           <t>Depreciation – Note 4</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E642" t="inlineStr">
         <is>
           <t>-</t>
@@ -72717,7 +72865,11 @@
           <t>Management fees – Note 11</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E644" t="inlineStr">
         <is>
           <t>-</t>
@@ -72810,7 +72962,11 @@
           <t>Professional fees – Note 11</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
@@ -73000,7 +73156,11 @@
           <t>Travel and promotion – Note 11</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E647" t="inlineStr">
         <is>
           <t>-</t>
@@ -73293,7 +73453,11 @@
           <t>Other income – Note 11</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E650" t="inlineStr">
         <is>
           <t>-</t>
@@ -73594,7 +73758,11 @@
           <t>Loss per share – basic and diluted – Note 10 $</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E653" t="inlineStr">
         <is>
           <t>-</t>
@@ -74087,7 +74255,11 @@
           <t>Other income – Note 11</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E658" t="inlineStr">
         <is>
           <t>-</t>
@@ -74382,7 +74554,11 @@
           <t>Loss per share – basic and diluted – Note 10 $</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
           <t>-</t>
@@ -74576,7 +74752,11 @@
           <t>Interest expense – Note 7</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E663" t="inlineStr">
         <is>
           <t>-</t>
@@ -74877,7 +75057,11 @@
           <t>Interest expense – Note 8</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E666" t="inlineStr">
         <is>
           <t>-</t>
@@ -75378,7 +75562,11 @@
           <t>Management fees – Note 13</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E671" t="inlineStr">
         <is>
           <t>-</t>
@@ -75477,7 +75665,11 @@
           <t>Professional fees – Note 13</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
           <t>-</t>
@@ -75675,7 +75867,11 @@
           <t>Travel and promotion – Note 13</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E674" t="inlineStr">
         <is>
           <t>-</t>
@@ -75774,7 +75970,11 @@
           <t>Interest expense – Note 9</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr"/>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E675" t="inlineStr">
         <is>
           <t>-</t>
@@ -76481,7 +76681,11 @@
           <t>Loss per share – basic and diluted – Note 12 $</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
           <t>-</t>
@@ -77077,7 +77281,11 @@
           <t>Management fees - Note 6</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E688" t="inlineStr">
         <is>
           <t>-</t>
@@ -77277,7 +77485,11 @@
           <t>Professional fees - Note 6</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E690" t="inlineStr">
         <is>
           <t>-</t>
@@ -77675,7 +77887,11 @@
           <t>Travel and promotion - Note 6</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr">
         <is>
           <t>-</t>
@@ -79178,7 +79394,11 @@
           <t>Management fees – Note 6</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E709" s="5" t="n">
         <v>0.27</v>
       </c>
@@ -79277,7 +79497,11 @@
           <t>Professional fees – Note 6</t>
         </is>
       </c>
-      <c r="D710" t="inlineStr"/>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E710" s="5" t="n">
         <v>0.118257</v>
       </c>
@@ -79578,7 +79802,11 @@
           <t>Travel and promotion – Note 6</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E713" s="5" t="n">
         <v>0.095319</v>
       </c>

--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -7014,19 +7014,19 @@
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -27219,7 +27219,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -31746,7 +31750,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -38059,7 +38067,11 @@
           <t>Proceeds on disposal of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATLE.xlsx
+++ b/output/pdf_financials_xlsx/ATLE.xlsx
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.564303</v>
+        <v>0.595268</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.560318</v>
+        <v>0.591283</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.296428</v>
+        <v>0.298928</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.266375</v>
+        <v>0.281375</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.259365</v>
+        <v>0.261865</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.269623</v>
+        <v>0.272123</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.260446</v>
+        <v>0.270446</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.262505</v>
+        <v>0.272505</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.214577</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.659622</v>
+        <v>0.690587</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.636703</v>
+        <v>0.667668</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.980818</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.659622</v>
+        <v>-0.690587</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.636703</v>
+        <v>-0.667668</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.980818</v>
@@ -1291,7 +1291,7 @@
         <v>-1.644564</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-44.56659</v>
+        <v>-42.986216</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-33.946</v>
@@ -1325,7 +1325,7 @@
         <v>3.214264</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.334858</v>
+        <v>-0.041</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1349,7 +1349,7 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.580374</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1606,10 +1606,10 @@
         <v>-13.029</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-3.919</v>
+        <v>-2.27</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>1.222</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="21">
@@ -1664,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-3.919</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="22">
@@ -1999,7 +1999,7 @@
         <v>-1.644564</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-44.501833</v>
+        <v>-42.921459</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-34.061</v>
@@ -2115,7 +2115,7 @@
         <v>-1.598173</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-42.333666</v>
+        <v>-40.753292</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-30.879</v>
@@ -2191,7 +2191,7 @@
         <v>-9449.376219476144</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-923509.2931937174</v>
+        <v>-889033.4205933682</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-308790</v>
@@ -2227,7 +2227,7 @@
         <v>-51.25168858370719</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-109.1126522407164</v>
+        <v>-1.341472033252801</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2251,7 +2251,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.676466893480459</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -4349,31 +4349,31 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.148327</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.153725</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.156025</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.136725</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.138024</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.139225</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.144225</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.145225</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.128326</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.006423</v>
+        <v>0.032925</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.005114</v>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.055459</v>
+        <v>-0.016111</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.209955</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.076516</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -30538,7 +30538,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -31352,7 +31356,11 @@
           <t>Proceeds from private placement 10</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -38875,7 +38883,11 @@
           <t>Deferred income tax recovery – Note 18</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -42124,7 +42136,11 @@
           <t>Net proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -47797,7 +47813,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -48813,7 +48833,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -50708,7 +50732,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>0.039348</v>
       </c>
@@ -51787,7 +51815,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -51888,7 +51920,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -57736,7 +57768,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -64863,7 +64899,11 @@
           <t>Deferred income tax recovery – Note 18</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -70978,7 +71018,11 @@
           <t>Directors’ fees – Note 10</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
@@ -72784,7 +72828,11 @@
           <t>Directors’ fees – Note 11</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -75374,7 +75422,11 @@
           <t>Directors’ fees – Note 13</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -76489,7 +76541,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E680" t="inlineStr">
         <is>
           <t>-</t>
@@ -77093,7 +77149,11 @@
           <t>Directors' fees - Note 6</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E686" t="inlineStr">
         <is>
           <t>-</t>
@@ -78701,7 +78761,11 @@
           <t>Future income tax recovery - Note 9</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E702" t="inlineStr">
         <is>
           <t>-</t>
@@ -79307,7 +79371,11 @@
           <t>Directors’ fees – Note 6</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E708" s="5" t="n">
         <v>0.030965</v>
       </c>
